--- a/chromadb/docs/ask.xlsx
+++ b/chromadb/docs/ask.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\onePal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75F4D6F-193A-4F01-AFC8-B26BFB0BF5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBD6EF6-53C9-4049-85FD-30C755ECF236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-1260" windowWidth="38620" windowHeight="21100" tabRatio="800" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="800" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidated" sheetId="13" r:id="rId1"/>
@@ -32,21 +32,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="448">
   <si>
     <t>Research schools that match your academic interests, financial situation, location preferences, and extracurricular opportunities. Consider visiting campuses and talking to current students.</t>
   </si>
@@ -1623,6 +1614,9 @@
   </si>
   <si>
     <t>Marks Grades GPA - What are the consequences of having a low GPA?</t>
+  </si>
+  <si>
+    <t>What are the social science courses I can take ?</t>
   </si>
 </sst>
 </file>
@@ -1994,2027 +1988,2027 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425CFC65-3725-4F63-BF18-A5D1EE9FCB3E}">
   <dimension ref="A1:A404"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="83.453125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="120" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="122" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="126" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="138" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="140" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="142" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="144" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="148" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="152" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="156" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="158" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="160" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="162" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="166" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="167" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="168" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="170" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="172" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="174" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="176" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="178" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="180" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="182" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="184" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="186" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="188" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="190" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="192" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="194" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="196" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="198" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="200" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="202" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="204" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="206" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="208" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="210" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="212" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="214" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A214" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="215" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="216" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="218" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="220" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A220" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="222" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A222" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="224" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A224" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="226" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A226" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="228" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="230" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A230" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A232" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="234" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="236" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A236" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="237" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="238" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="240" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="242" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A244" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="246" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="248" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="250" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A250" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="252" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A252" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="254" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="256" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="258" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A258" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="260" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A260" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="262" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A262" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A264" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="266" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="268" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="270" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="272" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A272" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="274" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A274" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="276" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A276" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="278" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A278" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="279" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="282" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="284" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A284" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="286" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A286" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="288" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A288" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="290" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="292" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A292" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="294" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A294" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="296" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A296" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="298" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="300" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="302" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="304" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:1" ht="116" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="306" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="308" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="310" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="312" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="313" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A313" s="8" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="314" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315" s="8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="316" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317" s="8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="318" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="319" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A319" s="8" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="320" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="321" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321" s="8" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="322" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="323" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A323" s="8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="324" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="325" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A325" s="8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="326" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="327" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A327" s="8" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="328" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="329" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A329" s="8" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="330" spans="1:1" ht="180" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" ht="174" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="331" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A331" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="332" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="333" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A333" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="334" spans="1:1" ht="375" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:1" ht="348" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="335" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A335" s="8" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="336" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="337" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A337" s="8" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="338" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="339" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A339" s="8" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="340" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="341" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A341" s="8" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="342" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A343" s="8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="344" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345" s="8" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="346" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347" s="8" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="348" spans="1:1" ht="180" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="349" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A349" s="8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="350" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="351" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:1" ht="87" x14ac:dyDescent="0.35">
       <c r="A351" s="8" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="353" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A353" s="8" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="354" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="355" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A355" s="8" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="356" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="357" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A357" s="8" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="358" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="359" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A359" s="8" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="360" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="361" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A361" s="8" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="362" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A363" s="8" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="364" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="365" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A365" s="8" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="366" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="367" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A367" s="8" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="368" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="369" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A369" s="8" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="370" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="371" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A371" s="8" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="372" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="373" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A373" s="8" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="374" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="375" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A375" s="8" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="376" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="377" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A377" s="8" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="378" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="379" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A379" s="8" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="380" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="381" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A381" s="8" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="382" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A383" s="8" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="384" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="385" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A385" s="8" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A387" s="8" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="388" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="389" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A389" s="8" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="390" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A390" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="391" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A391" s="8" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="392" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="393" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A393" s="8" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="394" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A394" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="395" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A395" s="8" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="396" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="397" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A397" s="8" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="398" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="399" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A399" s="8" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="400" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="401" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A401" s="8" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="402" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="403" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A403" s="8" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="404" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A404" s="3" t="s">
         <v>397</v>
       </c>
@@ -4034,17 +4028,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16402A52-5A6A-4D33-A9FD-2A06A339DE78}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.42578125" customWidth="1"/>
+    <col min="1" max="1" width="64.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>298</v>
       </c>
@@ -4057,47 +4051,47 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E1A4ED-233F-4C63-A88B-FAE3A3512625}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="63.140625" customWidth="1"/>
+    <col min="1" max="1" width="63.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>306</v>
       </c>
@@ -4110,17 +4104,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD72877-77C8-48F7-BD5F-803D7C6DFB15}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="101.85546875" customWidth="1"/>
+    <col min="1" max="1" width="101.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>308</v>
       </c>
@@ -4133,467 +4127,467 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3733348D-7DC1-4F77-B069-9BD6045C9209}">
   <dimension ref="A1:A92"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="142.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="142.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="240" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="203" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="87" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" s="8" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="8" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>397</v>
       </c>
@@ -4607,218 +4601,218 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A191"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="124.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="124.26953125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" s="6"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" s="6"/>
     </row>
   </sheetData>
@@ -4830,12 +4824,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15662940-B730-43B6-B08F-8951578B7AD9}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="142.140625" style="3" customWidth="1"/>
+    <col min="1" max="2" width="142.1796875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>148</v>
       </c>
@@ -4844,7 +4838,7 @@
         <v>AP - What are AP classes, and are they worth taking?</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -4853,7 +4847,7 @@
         <v>AP classes are advanced courses that can help you prepare for college-level work. They are often more challenging, but they can improve your college applications and earn you college credit if you score well on the AP exams.</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>155</v>
       </c>
@@ -4862,7 +4856,7 @@
         <v>AP - How do AP tests affect my college applications?</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
@@ -4871,7 +4865,7 @@
         <v>AP tests can show colleges that you are capable of handling rigorous coursework. High scores may also lead to college credit or placement in advanced courses.</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>162</v>
       </c>
@@ -4880,7 +4874,7 @@
         <v>AP - What AP classes should I take?</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
@@ -4889,7 +4883,7 @@
         <v>Choose AP classes that align with your interests and potential college major. You should also consider your workload and how well you feel you can manage advanced courses.</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>169</v>
       </c>
@@ -4898,7 +4892,7 @@
         <v>AP - How do I register for an AP class?</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
@@ -4907,7 +4901,7 @@
         <v>Registration for AP classes typically happens during course selection in the spring. Speak with your counselor to make sure you’re enrolled in the courses you want.</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>176</v>
       </c>
@@ -4916,7 +4910,7 @@
         <v>AP - How do I register for the AP exams?</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
@@ -4925,7 +4919,7 @@
         <v>AP exams are typically registered for through your school, often by the fall of the year you plan to take the exam. Check with your counselor for deadlines and procedures.</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>183</v>
       </c>
@@ -4934,7 +4928,7 @@
         <v>AP - What are the benefits of taking AP classes?</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -4943,7 +4937,7 @@
         <v>AP classes help you develop college-level academic skills, improve your GPA (if your school offers weighted grades), and can result in college credit for high scores on AP exams.</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>190</v>
       </c>
@@ -4952,7 +4946,7 @@
         <v>AP - What if I don’t do well in an AP class?</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
@@ -4961,7 +4955,7 @@
         <v>It’s important to talk to your teacher for extra help or tutoring. If it’s too overwhelming, consider whether switching to a regular course is a better option. Your mental health and well-being are also priorities.</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>197</v>
       </c>
@@ -4970,7 +4964,7 @@
         <v>AP - How do AP exams impact my GPA?</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>27</v>
       </c>
@@ -4979,7 +4973,7 @@
         <v>Some schools offer weighted GPA for AP courses, meaning you’ll earn extra points for grades in those classes. However, AP exam scores don’t directly affect your GPA, though they can impact your college applications.</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>204</v>
       </c>
@@ -4988,7 +4982,7 @@
         <v>AP - How do I prepare for the AP exams?</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -4997,7 +4991,7 @@
         <v>Begin studying well in advance, review your class materials, take practice exams, and use study guides. Forming or joining a study group can also help reinforce concepts.</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>288</v>
       </c>
@@ -5006,7 +5000,7 @@
         <v>AP - When are AP exams held?</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -5015,7 +5009,7 @@
         <v>AP exams are typically held in May. Check the specific dates each year on the College Board website or with your counselor to ensure you're prepared.</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>281</v>
       </c>
@@ -5024,7 +5018,7 @@
         <v>AP - What should I do if I’m struggling in an AP class?</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>30</v>
       </c>
@@ -5033,7 +5027,7 @@
         <v>Talk to your teacher for help, seek tutoring, and consider using online resources or review books. Organize study time to focus on areas where you need the most improvement.</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>274</v>
       </c>
@@ -5042,7 +5036,7 @@
         <v>AP - Can I drop an AP class if it’s too hard?</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>31</v>
       </c>
@@ -5051,7 +5045,7 @@
         <v>Yes, but you should talk to your counselor first to understand the implications, especially regarding your GPA and how dropping the class may affect your overall schedule.</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>267</v>
       </c>
@@ -5060,7 +5054,7 @@
         <v>AP - Are AP tests mandatory?</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>32</v>
       </c>
@@ -5069,7 +5063,7 @@
         <v>AP tests are not mandatory, but if you’re enrolled in an AP class, you are encouraged to take the exam to potentially earn college credit and enhance your application.</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>260</v>
       </c>
@@ -5078,7 +5072,7 @@
         <v>AP - What if I don’t pass the AP exam?</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
@@ -5087,7 +5081,7 @@
         <v>A low score won’t hurt your high school GPA. Many colleges may not grant credit for lower scores, but it’s still a learning experience. Focus on your performance in the class.</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>253</v>
       </c>
@@ -5096,7 +5090,7 @@
         <v>AP - How do I balance AP classes with other extracurricular activities?</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
@@ -5105,7 +5099,7 @@
         <v>Time management is key. Prioritize your tasks, create a study schedule, and learn to say no to overcommitting. It’s important to find balance between academics and personal activities.</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>246</v>
       </c>
@@ -5114,7 +5108,7 @@
         <v>AP - Do AP classes help with college admissions?</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
@@ -5123,7 +5117,7 @@
         <v>Yes, taking AP classes demonstrates to colleges that you are ready for the academic challenges of college. A rigorous course load can make your application stand out.</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>239</v>
       </c>
@@ -5132,7 +5126,7 @@
         <v>AP - How do I get AP credit in college?</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
@@ -5141,7 +5135,7 @@
         <v>AP credit is granted by some colleges based on your score on the AP exam. Typically, a score of 3 or higher is required, though some schools may require a 4 or 5 for credit.</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>232</v>
       </c>
@@ -5150,7 +5144,7 @@
         <v>AP - What if I don’t want to take the AP exam after enrolling in the class?</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
@@ -5159,7 +5153,7 @@
         <v>It’s usually not required to take the AP exam, but you should check with your school to see if there are any consequences or fees for not taking the exam.</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>226</v>
       </c>
@@ -5168,7 +5162,7 @@
         <v>AP - How much time should I spend studying for AP exams?</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -5177,7 +5171,7 @@
         <v>The amount of time varies by subject and your comfort level with the material. Generally, it’s recommended to study for at least 1-2 hours a day in the month leading up to the exam.</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>221</v>
       </c>
@@ -5186,7 +5180,7 @@
         <v>AP - Can AP classes help with my college major?</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
@@ -5195,7 +5189,7 @@
         <v>Yes, AP classes that align with your intended major (such as AP Biology for a future in medicine or AP Calculus for engineering) can prepare you for college-level courses in that field and may even provide you with college credit in the subject.</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>333</v>
       </c>
@@ -5204,7 +5198,7 @@
         <v>AP - Can I take an AP exam without taking the course?</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>334</v>
       </c>
@@ -5224,12 +5218,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D072C77-B6CD-40F4-8EAA-A2768906B2C5}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultColWidth="109" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="109" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="109" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>149</v>
       </c>
@@ -5238,7 +5232,7 @@
         <v>Marks Grades GPA - What is GPA, and why is it important?</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -5247,7 +5241,7 @@
         <v>GPA (Grade Point Average) is a numerical representation of your academic performance. It’s important because it’s used by colleges, employers, and scholarship committees to assess your academic abilities.</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>156</v>
       </c>
@@ -5256,7 +5250,7 @@
         <v>Marks Grades GPA - How is my GPA calculated?</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
@@ -5265,7 +5259,7 @@
         <v>Your GPA is calculated by averaging the grades you earn in all your classes. Each grade is assigned a point value (e.g., A = 4.0, B = 3.0) and then averaged over your classes.</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>163</v>
       </c>
@@ -5274,7 +5268,7 @@
         <v>Marks Grades GPA - How does weighted GPA work?</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
@@ -5283,7 +5277,7 @@
         <v>A weighted GPA gives extra points for advanced courses like AP or honors classes. For example, an A in an AP class might count as 5.0 instead of 4.0.</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>170</v>
       </c>
@@ -5292,7 +5286,7 @@
         <v>Marks Grades GPA - Can my GPA go above a 4.0?</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -5301,7 +5295,7 @@
         <v>Yes, if you take weighted courses (like AP or honors classes), your GPA can exceed 4.0 depending on how well you perform in those classes.</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>177</v>
       </c>
@@ -5310,7 +5304,7 @@
         <v>Marks Grades GPA - How do I raise my GPA?</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
@@ -5319,7 +5313,7 @@
         <v>Focus on improving your grades in current and future courses. Prioritize studying, ask for help when needed, and stay organized to avoid missing assignments or deadlines.</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>184</v>
       </c>
@@ -5328,7 +5322,7 @@
         <v>Marks Grades GPA - How can I improve my grades in a class I’m struggling with?</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
@@ -5337,7 +5331,7 @@
         <v>Speak with your teacher for additional help, consider extra credit opportunities if available, and use tutoring or study groups. It’s important to catch up on assignments and stay consistent.</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>191</v>
       </c>
@@ -5346,7 +5340,7 @@
         <v>Marks Grades GPA - Can I retake a class to improve my GPA?</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>46</v>
       </c>
@@ -5355,7 +5349,7 @@
         <v>Fulton County does not offer “repeat to replace.” All failing grades will remain on the transcript.   Consult with your counselor and/or the graduation coach about which option is best for you if you want to improve your GPA.</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>198</v>
       </c>
@@ -5364,7 +5358,7 @@
         <v>Marks Grades GPA - Does an F affect my GPA?</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>47</v>
       </c>
@@ -5373,7 +5367,7 @@
         <v>Yes, an F will lower your GPA. It’s important to work with your teacher and counselor to understand how to improve or retake the course if necessary.</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>205</v>
       </c>
@@ -5382,7 +5376,7 @@
         <v>Marks Grades GPA - What’s the difference between weighted and unweighted GPA?</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>48</v>
       </c>
@@ -5391,7 +5385,7 @@
         <v>Weighted GPA includes extra points for AP, honors, and college-level courses, while unweighted GPA treats all courses the same, typically on a scale of 4.0.</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>289</v>
       </c>
@@ -5400,7 +5394,7 @@
         <v>Marks Grades GPA - How do colleges view my GPA?</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>49</v>
       </c>
@@ -5409,7 +5403,7 @@
         <v>Colleges use your GPA to assess how well you’ve performed academically. They may look at both your weighted and unweighted GPA, but a higher GPA generally improves your chances for admission.</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>282</v>
       </c>
@@ -5418,7 +5412,7 @@
         <v>Marks Grades GPA - Can extra credit improve my GPA?</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>50</v>
       </c>
@@ -5427,7 +5421,7 @@
         <v>Yes, extra credit assignments can help raise your grade in a particular class, which can improve your GPA, but it’s important to not rely solely on extra credit to boost your grades.</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>275</v>
       </c>
@@ -5436,7 +5430,7 @@
         <v>Marks Grades GPA - How much will a single bad grade affect my GPA?</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>51</v>
       </c>
@@ -5445,7 +5439,7 @@
         <v>It depends on your overall GPA and the weight of the class. One bad grade may have a significant impact if it’s in a core class or if you don’t have many other courses to balance it out.</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>268</v>
       </c>
@@ -5454,7 +5448,7 @@
         <v>Marks Grades GPA - Should I drop a class if I’m getting a low grade?</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>52</v>
       </c>
@@ -5463,7 +5457,7 @@
         <v>If you’re struggling, talk to your counselor. Dropping the class might be an option, but be sure to consider how it affects your GPA and graduation requirements.</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>261</v>
       </c>
@@ -5472,7 +5466,7 @@
         <v>Marks Grades GPA - How can I balance high grades with extracurriculars?</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>53</v>
       </c>
@@ -5481,7 +5475,7 @@
         <v>Time management is key. Create a study schedule, set priorities, and avoid overloading yourself with extracurriculars that could negatively impact your academic performance.</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>254</v>
       </c>
@@ -5490,7 +5484,7 @@
         <v>Marks Grades GPA - What should I do if my GPA is lower than I hoped for?</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>54</v>
       </c>
@@ -5499,7 +5493,7 @@
         <v>Focus on improving grades in future semesters and seek help in areas where you’re struggling. Colleges often look at trends in your grades (e.g., an upward trajectory) rather than just one low GPA.</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>247</v>
       </c>
@@ -5508,7 +5502,7 @@
         <v>Marks Grades GPA - What is a good GPA for getting into college?</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>55</v>
       </c>
@@ -5517,7 +5511,7 @@
         <v>A good GPA depends on the colleges you are applying to. Highly selective schools often look for a GPA of 3.7 or higher, while other colleges may accept GPAs of 3.0 or above.</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>240</v>
       </c>
@@ -5526,7 +5520,7 @@
         <v>Marks Grades GPA - How can I calculate my GPA during the semester?</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>56</v>
       </c>
@@ -5535,7 +5529,7 @@
         <v>You can calculate your GPA by assigning point values to your grades, multiplying those values by the number of credits for each class, and averaging the results.</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>233</v>
       </c>
@@ -5544,7 +5538,7 @@
         <v>Marks Grades GPA - Can my GPA improve if I take summer school classes?</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>57</v>
       </c>
@@ -5553,7 +5547,7 @@
         <v>Yes, taking summer school classes and earning higher grades can help improve your GPA. However, the courses must be accepted by your school for credit.</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>227</v>
       </c>
@@ -5562,7 +5556,7 @@
         <v>Marks Grades GPA - How do I deal with a low GPA when applying to college?</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>58</v>
       </c>
@@ -5571,7 +5565,7 @@
         <v>Focus on other aspects of your application, such as your extracurricular activities, personal essay, and letters of recommendation. You can also explain any extenuating circumstances in your application.</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>222</v>
       </c>
@@ -5580,7 +5574,7 @@
         <v>Marks Grades GPA - What are the consequences of having a low GPA?</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>59</v>
       </c>
@@ -5597,307 +5591,307 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2472288A-9F54-4634-9FFB-FAB4383069BC}">
   <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="113.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="113.54296875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>89</v>
       </c>
@@ -5914,207 +5908,207 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADC1432-AAF4-44FC-AEEB-13920F8EF196}">
   <dimension ref="A1:A40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="99.85546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="99.81640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>109</v>
       </c>
@@ -6128,377 +6122,377 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273ED2C6-9AC2-4335-92C1-081EEDA77A70}">
   <dimension ref="A1:A74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="83.26953125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>146</v>
       </c>
@@ -6514,17 +6508,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A1146E1-BF6D-4105-BC50-43605A6E69FA}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="60.42578125" customWidth="1"/>
+    <col min="1" max="1" width="60.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>295</v>
       </c>
@@ -6537,17 +6531,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE8F1516-F4E2-4F52-A7A6-F664BF978720}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="66.140625" customWidth="1"/>
+    <col min="1" max="1" width="66.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>297</v>
       </c>
